--- a/data/trans_orig/IP16_n_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Edad-trans_orig.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,42 +1680,42 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6374</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>6,77%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6360</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>44401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62821</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>24169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>36553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61837</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>82124</t>
+          <t>81545</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>106924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>39406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48733</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96249</t>
+          <t>96466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>109731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8248,12 +8248,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -8359,12 +8359,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>44417</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41360</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9081,47 +9081,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>75214</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>69570</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>79140</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>81,53%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>75214</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>69440</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>79066</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -9592,12 +9592,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9753,12 +9753,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>56507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42827</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -10936,12 +10936,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -11047,12 +11047,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11062,12 +11062,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -11840,12 +11840,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -11951,12 +11951,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -12512,12 +12512,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12547,12 +12547,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -12623,12 +12623,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13047,12 +13047,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -13073,12 +13073,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13234,12 +13234,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -13295,12 +13295,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13330,12 +13330,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13345,12 +13345,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13380,12 +13380,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -13856,12 +13856,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13926,12 +13926,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -13967,12 +13967,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73997</t>
+          <t>74355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>50711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97641</t>
+          <t>97582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>124651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14391,12 +14391,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -14417,12 +14417,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14543,12 +14543,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14613,12 +14613,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -14639,12 +14639,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
